--- a/result/morris/morris_first_inf_ONLY_Signed_N256_seed42.xlsx
+++ b/result/morris/morris_first_inf_ONLY_Signed_N256_seed42.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,33 +453,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>infection__infection_condition</t>
+          <t>zoospore_alive__vpd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.18478732638889</v>
+        <v>-23.01757812500002</v>
       </c>
       <c r="C2" t="n">
-        <v>30.8505859375</v>
+        <v>26.43120659722224</v>
       </c>
       <c r="D2" t="n">
-        <v>22.15828506737807</v>
+        <v>28.74672260293747</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zoospore_alive__vpd</t>
+          <t>infection__infection_condition</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-24.80750868055556</v>
+        <v>19.48643663194445</v>
       </c>
       <c r="C3" t="n">
-        <v>27.2951388888889</v>
+        <v>22.40635850694444</v>
       </c>
       <c r="D3" t="n">
-        <v>29.67463381949971</v>
+        <v>23.77190627810535</v>
       </c>
     </row>
     <row r="4">
@@ -489,29 +489,29 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.4763454861111</v>
+        <v>14.07259114583333</v>
       </c>
       <c r="C4" t="n">
-        <v>26.02061631944444</v>
+        <v>20.62402343749999</v>
       </c>
       <c r="D4" t="n">
-        <v>34.17476463004962</v>
+        <v>30.9645915996064</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mp_tmp__rh_wet_night</t>
+          <t>thresholds__min_spores</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.14474826388888</v>
+        <v>10.47005208333334</v>
       </c>
       <c r="C5" t="n">
-        <v>23.05208333333333</v>
+        <v>19.15755208333334</v>
       </c>
       <c r="D5" t="n">
-        <v>24.90868402726788</v>
+        <v>25.30001227328761</v>
       </c>
     </row>
     <row r="6">
@@ -521,125 +521,141 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.3154296874999993</v>
+        <v>-3.199001736111112</v>
       </c>
       <c r="C6" t="n">
-        <v>7.678276909722221</v>
+        <v>10.29882812500001</v>
       </c>
       <c r="D6" t="n">
-        <v>17.98575671140348</v>
+        <v>18.35434139233951</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sporulation__MP_min</t>
+          <t>mp_tmp__rh_wet_night</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.520399305555555</v>
+        <v>6.134331597222221</v>
       </c>
       <c r="C7" t="n">
-        <v>3.163628472222222</v>
+        <v>9.894748263888896</v>
       </c>
       <c r="D7" t="n">
-        <v>8.365689533435123</v>
+        <v>15.75416982351577</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sporulation__Topt</t>
+          <t>dispersal__wind_min</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.3330078125</v>
+        <v>-1.673611111111111</v>
       </c>
       <c r="C8" t="n">
-        <v>3.045247395833334</v>
+        <v>6.749999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>10.72413838252652</v>
+        <v>17.03208788349997</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dispersal__wind_min</t>
+          <t>sporulation__Topt</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.590603298611111</v>
+        <v>-2.025716145833334</v>
       </c>
       <c r="C9" t="n">
-        <v>2.835828993055557</v>
+        <v>4.479709201388892</v>
       </c>
       <c r="D9" t="n">
-        <v>8.254013471953764</v>
+        <v>10.52320285479559</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>incubation__spl_end</t>
+          <t>zoospore_alive__rain</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.807183159722221</v>
+        <v>1.117513020833333</v>
       </c>
       <c r="C10" t="n">
-        <v>2.807183159722221</v>
+        <v>3.9560546875</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4325901435652717</v>
+        <v>16.22019932868382</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>deposition__rain_min</t>
+          <t>sporulation__Tmin</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.474066840277778</v>
+        <v>-0.912109375</v>
       </c>
       <c r="C11" t="n">
-        <v>2.6455078125</v>
+        <v>2.981119791666668</v>
       </c>
       <c r="D11" t="n">
-        <v>9.473387323979777</v>
+        <v>9.666057988840043</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sporulation__Tmin</t>
+          <t>incubation__spl_end</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5206163194444444</v>
+        <v>2.770399305555556</v>
       </c>
       <c r="C12" t="n">
-        <v>2.502604166666667</v>
+        <v>2.770399305555556</v>
       </c>
       <c r="D12" t="n">
-        <v>10.63972618313855</v>
+        <v>0.417772452438479</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>zoospore_alive__rain</t>
+          <t>deposition__rain_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6981336805555556</v>
+        <v>1.530815972222223</v>
       </c>
       <c r="C13" t="n">
-        <v>1.616319444444444</v>
+        <v>2.223958333333333</v>
       </c>
       <c r="D13" t="n">
-        <v>4.666428527866437</v>
+        <v>7.088957982444972</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sporulation__MP_min</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.083116319444444</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.395616319444445</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.739181383436327</v>
       </c>
     </row>
   </sheetData>
